--- a/reports/scan/github_cbg.xlsx
+++ b/reports/scan/github_cbg.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -597,9 +597,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -659,9 +659,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -674,9 +674,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">

--- a/reports/scan/github_cbg.xlsx
+++ b/reports/scan/github_cbg.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -703,47 +703,47 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -780,17 +780,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -860,9 +860,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">

--- a/reports/scan/github_cbg.xlsx
+++ b/reports/scan/github_cbg.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
         <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -72,13 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,12 +556,12 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -624,7 +618,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -684,9 +678,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -723,32 +717,32 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -770,52 +764,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -847,32 +841,32 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
